--- a/PSCBOX_DIAPHRAGM_P1.xlsx
+++ b/PSCBOX_DIAPHRAGM_P1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,26 +1157,2028 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t># ================= REBAR — 다음 단계 =================</t>
+          <t># ================= DUCT · 매입물 (8-244 벡터) =================</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>#  면 철근망 : srebar code 1 (곧은 철근 열차 — 자리에서 태어나 양쪽으로 자라다 처음 만나는 피복선에서 멈춘다)</t>
+          <t># duct | id | shape | D | H | x | y | ref | clr        (문법은 bim_duct.js)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>#  개구부    : 개구부 면은 피복면(인력장)이다 — 철근망은 거기서 멈추므로 저절로 잘린다 · M1~M3 는 그 면에 앉는다</t>
+          <t>#   8-244 에서 원을 전부 찾아 셋으로 갈랐다 :</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
+        <is>
+          <t>#     자홍 ⊕ Ø 111.7~111.8  46 개 — 상부슬래브의 종방향 강연선 덕트. 상면에서 깊이 160 · 310 (두 줄)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>#     적색 ○ Ø 101.6         8 개 — 상부슬래브 바로 밑 격벽 안. 상면에서 깊이 940. **용도는 도면에 없다**</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>#                                    (슬리브 · 임시 강봉 등) — 철근이 피해야 할 매입물로 넣는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>#     적색 ○ Ø 239          — 철근 번호 말풍선 (12) (M1) … 덕트가 아니다. 넣지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>#   깊이는 데크 -3% 면에서 잰다 (ref deck). 좌우 대칭 — 왼쪽 · 오른쪽 위치가 1 mm 안에서 같다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>#   같은 다리의 S14 (주두부 옆 세그먼트) 는 이 두 줄에 한쪽 8 + 2 개다 — 주두부에 덕트가 훨씬 많다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>#   단면 외형이 같아도 덕트 배치는 자리마다 다르다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>#   ! 외경은 벡터로 잰 값(112 · 102). S14 는 픽셀로 재서 120 으로 넣었다(±10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>#   clr 25 는 S14 와 같다 (도면에 순간격 표기 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t># --- 상단 열 : 상면에서 160 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AL1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>112</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>-1255</v>
+      </c>
+      <c r="G72" t="n">
+        <v>160</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AL2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>112</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>-1405</v>
+      </c>
+      <c r="G73" t="n">
+        <v>160</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AL3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>112</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>-1555</v>
+      </c>
+      <c r="G74" t="n">
+        <v>160</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AL4</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>112</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>-1755</v>
+      </c>
+      <c r="G75" t="n">
+        <v>160</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AL5</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>112</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>-1905</v>
+      </c>
+      <c r="G76" t="n">
+        <v>160</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AL6</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>112</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>-2055</v>
+      </c>
+      <c r="G77" t="n">
+        <v>160</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AL7</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>112</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>-2345</v>
+      </c>
+      <c r="G78" t="n">
+        <v>160</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AL8</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>112</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>-2625</v>
+      </c>
+      <c r="G79" t="n">
+        <v>160</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AL9</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>112</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>-2915</v>
+      </c>
+      <c r="G80" t="n">
+        <v>160</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AL10</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>112</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>-3585</v>
+      </c>
+      <c r="G81" t="n">
+        <v>160</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AL11</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>112</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>-3885</v>
+      </c>
+      <c r="G82" t="n">
+        <v>160</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AL12</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>112</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>-4185</v>
+      </c>
+      <c r="G83" t="n">
+        <v>160</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AL13</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>112</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>-4335</v>
+      </c>
+      <c r="G84" t="n">
+        <v>160</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>AL14</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>112</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>-4485</v>
+      </c>
+      <c r="G85" t="n">
+        <v>160</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AL15</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>112</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>-4685</v>
+      </c>
+      <c r="G86" t="n">
+        <v>160</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>AL16</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>112</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>-4835</v>
+      </c>
+      <c r="G87" t="n">
+        <v>160</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>AL17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>112</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>-4985</v>
+      </c>
+      <c r="G88" t="n">
+        <v>160</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>AR1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>112</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>1255</v>
+      </c>
+      <c r="G89" t="n">
+        <v>160</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AR2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>112</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>1405</v>
+      </c>
+      <c r="G90" t="n">
+        <v>160</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>AR3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>112</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>1555</v>
+      </c>
+      <c r="G91" t="n">
+        <v>160</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AR4</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>112</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G92" t="n">
+        <v>160</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AR5</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>112</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>1905</v>
+      </c>
+      <c r="G93" t="n">
+        <v>160</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>AR6</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>112</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>2055</v>
+      </c>
+      <c r="G94" t="n">
+        <v>160</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AR7</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>112</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>2345</v>
+      </c>
+      <c r="G95" t="n">
+        <v>160</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AR8</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>112</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
+        <v>2625</v>
+      </c>
+      <c r="G96" t="n">
+        <v>160</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>AR9</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>112</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>2915</v>
+      </c>
+      <c r="G97" t="n">
+        <v>160</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AR10</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>112</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="n">
+        <v>3585</v>
+      </c>
+      <c r="G98" t="n">
+        <v>160</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>AR11</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>112</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G99" t="n">
+        <v>160</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>AR12</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>112</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="n">
+        <v>4185</v>
+      </c>
+      <c r="G100" t="n">
+        <v>160</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>AR13</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>112</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="n">
+        <v>4335</v>
+      </c>
+      <c r="G101" t="n">
+        <v>160</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>AR14</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>112</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>4485</v>
+      </c>
+      <c r="G102" t="n">
+        <v>160</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AR15</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>112</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="n">
+        <v>4685</v>
+      </c>
+      <c r="G103" t="n">
+        <v>160</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AR16</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>112</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="n">
+        <v>4835</v>
+      </c>
+      <c r="G104" t="n">
+        <v>160</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>AR17</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>112</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>4985</v>
+      </c>
+      <c r="G105" t="n">
+        <v>160</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t># --- 하단 열 : 상면에서 310 ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BL1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>112</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>-2055</v>
+      </c>
+      <c r="G107" t="n">
+        <v>310</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BL2</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>112</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="n">
+        <v>-2345</v>
+      </c>
+      <c r="G108" t="n">
+        <v>310</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BL3</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>112</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>-2625</v>
+      </c>
+      <c r="G109" t="n">
+        <v>310</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BL4</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>112</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="n">
+        <v>-3885</v>
+      </c>
+      <c r="G110" t="n">
+        <v>310</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BL5</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>112</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>-4185</v>
+      </c>
+      <c r="G111" t="n">
+        <v>310</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>BL6</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>112</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="n">
+        <v>-4335</v>
+      </c>
+      <c r="G112" t="n">
+        <v>310</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>BR1</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>112</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="n">
+        <v>2055</v>
+      </c>
+      <c r="G113" t="n">
+        <v>310</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>BR2</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>112</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="n">
+        <v>2345</v>
+      </c>
+      <c r="G114" t="n">
+        <v>310</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BR3</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>112</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="n">
+        <v>2625</v>
+      </c>
+      <c r="G115" t="n">
+        <v>310</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>BR4</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>112</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G116" t="n">
+        <v>310</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BR5</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>112</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="n">
+        <v>4185</v>
+      </c>
+      <c r="G117" t="n">
+        <v>310</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BR6</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>112</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="n">
+        <v>4335</v>
+      </c>
+      <c r="G118" t="n">
+        <v>310</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t># --- 매입물 : 상면에서 940 (용도 미확인) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EL1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>102</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="n">
+        <v>-1100</v>
+      </c>
+      <c r="G120" t="n">
+        <v>940</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EL2</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>102</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="n">
+        <v>-1540</v>
+      </c>
+      <c r="G121" t="n">
+        <v>940</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>EL3</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>102</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="n">
+        <v>-1900</v>
+      </c>
+      <c r="G122" t="n">
+        <v>940</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>EL4</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>102</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="n">
+        <v>-2290</v>
+      </c>
+      <c r="G123" t="n">
+        <v>940</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>ER1</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>102</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="n">
+        <v>1100</v>
+      </c>
+      <c r="G124" t="n">
+        <v>940</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>ER2</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>102</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="n">
+        <v>1540</v>
+      </c>
+      <c r="G125" t="n">
+        <v>940</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ER3</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>102</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="n">
+        <v>1900</v>
+      </c>
+      <c r="G126" t="n">
+        <v>940</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ER4</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>102</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="n">
+        <v>2290</v>
+      </c>
+      <c r="G127" t="n">
+        <v>940</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t># ================= REBAR — 다음 단계 =================</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>#  면 철근망 : srebar code 1 (곧은 철근 열차 — 자리에서 태어나 양쪽으로 자라다 처음 만나는 피복선에서 멈춘다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>#  개구부    : 개구부 면은 피복면(인력장)이다 — 철근망은 거기서 멈추므로 저절로 잘린다 · M1~M3 는 그 면에 앉는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>end</t>
         </is>
